--- a/helper_data/numbers_helper.xlsx
+++ b/helper_data/numbers_helper.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fhnw365-my.sharepoint.com/personal/jan_zwicky_fhnw_ch/Documents/Text-To-Speech/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="456" documentId="8_{6B35F0C3-DE9F-4521-9181-E1BEE38A111A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0516CCFE-63DF-4679-B14D-32FAA2C5D799}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C30FDE-AC1F-4AEA-9636-4592EA59F011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="11646" yWindow="1848" windowWidth="17280" windowHeight="10038" activeTab="3" xr2:uid="{102AC6CB-56E7-4332-8A21-1A395C83D910}"/>
+    <workbookView xWindow="38280" yWindow="2355" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{102AC6CB-56E7-4332-8A21-1A395C83D910}"/>
   </bookViews>
   <sheets>
     <sheet name="Numbers" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,11 @@
     <sheet name="Ordinal_deklination" sheetId="3" r:id="rId4"/>
     <sheet name="Cities" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Numbers!$A$1:$D$52</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="400">
   <si>
     <t>Nummerisch/ Beispiel</t>
   </si>
@@ -1153,6 +1157,105 @@
   </si>
   <si>
     <t>St_Gallen_short</t>
+  </si>
+  <si>
+    <t>Sekunden</t>
+  </si>
+  <si>
+    <t>Sekundä</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eis </t>
+  </si>
+  <si>
+    <t>foif</t>
+  </si>
+  <si>
+    <t>sachs</t>
+  </si>
+  <si>
+    <t>zah</t>
+  </si>
+  <si>
+    <t>drizah</t>
+  </si>
+  <si>
+    <t>vierzah</t>
+  </si>
+  <si>
+    <t>füfzah</t>
+  </si>
+  <si>
+    <t>sachszah</t>
+  </si>
+  <si>
+    <t>sibzah</t>
+  </si>
+  <si>
+    <t>achtzah</t>
+  </si>
+  <si>
+    <t>nünzah</t>
+  </si>
+  <si>
+    <t>sachzg</t>
+  </si>
+  <si>
+    <t>sibezg</t>
+  </si>
+  <si>
+    <t>foifedachzg</t>
+  </si>
+  <si>
+    <t>hunderzweiedriisg</t>
+  </si>
+  <si>
+    <t>sachstuusigdrühundertdrüevierzg</t>
+  </si>
+  <si>
+    <t>zahtuusig</t>
+  </si>
+  <si>
+    <t>tuusigste</t>
+  </si>
+  <si>
+    <t>Er chunt als ersts is ziel</t>
+  </si>
+  <si>
+    <t>Sie isch erschti worde</t>
+  </si>
+  <si>
+    <t>Er isch ufem erste platz</t>
+  </si>
+  <si>
+    <t>zani</t>
+  </si>
+  <si>
+    <t>sibni</t>
+  </si>
+  <si>
+    <t>sachsi</t>
+  </si>
+  <si>
+    <t>foifi</t>
+  </si>
+  <si>
+    <t>Septamber</t>
+  </si>
+  <si>
+    <t>Novamber</t>
+  </si>
+  <si>
+    <t>Dezamber</t>
+  </si>
+  <si>
+    <t>Sekunde</t>
+  </si>
+  <si>
+    <t>Sibte</t>
+  </si>
+  <si>
+    <t>Zürich_short</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1293,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1224,11 +1327,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1237,6 +1349,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1254,10 +1369,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1577,15 +1688,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0D0A95-DEDA-4243-943F-4F8F00442EF6}">
-  <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:D52"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.05078125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.3671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.578125" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1595,8 +1706,11 @@
       <c r="C1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1606,8 +1720,11 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -1617,8 +1734,11 @@
       <c r="C3" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1628,8 +1748,11 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1639,8 +1762,11 @@
       <c r="C5" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1650,8 +1776,11 @@
       <c r="C6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1661,8 +1790,11 @@
       <c r="C7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1672,8 +1804,11 @@
       <c r="C8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>4</v>
       </c>
@@ -1683,8 +1818,11 @@
       <c r="C9" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>5</v>
       </c>
@@ -1694,8 +1832,11 @@
       <c r="C10" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>6</v>
       </c>
@@ -1705,8 +1846,11 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>7</v>
       </c>
@@ -1716,8 +1860,11 @@
       <c r="C12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>8</v>
       </c>
@@ -1727,8 +1874,11 @@
       <c r="C13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>9</v>
       </c>
@@ -1738,8 +1888,11 @@
       <c r="C14" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>10</v>
       </c>
@@ -1749,8 +1902,11 @@
       <c r="C15" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D15" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>11</v>
       </c>
@@ -1760,8 +1916,11 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>12</v>
       </c>
@@ -1771,8 +1930,11 @@
       <c r="C17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>13</v>
       </c>
@@ -1782,8 +1944,11 @@
       <c r="C18" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D18" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1793,8 +1958,11 @@
       <c r="C19" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D19" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1804,8 +1972,11 @@
       <c r="C20" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D20" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1815,8 +1986,11 @@
       <c r="C21" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D21" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1826,8 +2000,11 @@
       <c r="C22" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D22" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1837,8 +2014,11 @@
       <c r="C23" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1848,8 +2028,11 @@
       <c r="C24" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20</v>
       </c>
@@ -1859,8 +2042,11 @@
       <c r="C25" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>30</v>
       </c>
@@ -1870,8 +2056,11 @@
       <c r="C26" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>40</v>
       </c>
@@ -1881,8 +2070,11 @@
       <c r="C27" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>50</v>
       </c>
@@ -1892,8 +2084,11 @@
       <c r="C28" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>60</v>
       </c>
@@ -1903,8 +2098,11 @@
       <c r="C29" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D29" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>70</v>
       </c>
@@ -1914,8 +2112,11 @@
       <c r="C30" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D30" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>80</v>
       </c>
@@ -1925,8 +2126,11 @@
       <c r="C31" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>90</v>
       </c>
@@ -1936,8 +2140,11 @@
       <c r="C32" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>85</v>
       </c>
@@ -1947,8 +2154,11 @@
       <c r="C33" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D33" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>100</v>
       </c>
@@ -1958,8 +2168,11 @@
       <c r="C34" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>132</v>
       </c>
@@ -1969,8 +2182,11 @@
       <c r="C35" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D35" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>200</v>
       </c>
@@ -1980,8 +2196,11 @@
       <c r="C36" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1000</v>
       </c>
@@ -1991,8 +2210,11 @@
       <c r="C37" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>6343</v>
       </c>
@@ -2002,8 +2224,11 @@
       <c r="C38" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D38" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>10000</v>
       </c>
@@ -2013,8 +2238,11 @@
       <c r="C39" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D39" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -2024,8 +2252,11 @@
       <c r="C40" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2035,8 +2266,11 @@
       <c r="C41" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -2046,8 +2280,11 @@
       <c r="C42" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
@@ -2057,8 +2294,11 @@
       <c r="C43" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
@@ -2068,8 +2308,11 @@
       <c r="C44" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>49</v>
       </c>
@@ -2079,8 +2322,11 @@
       <c r="C45" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D45" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
@@ -2090,8 +2336,11 @@
       <c r="C46" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
@@ -2101,8 +2350,11 @@
       <c r="C47" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>63</v>
       </c>
@@ -2112,8 +2364,11 @@
       <c r="C48" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D48" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>65</v>
       </c>
@@ -2123,8 +2378,11 @@
       <c r="C49" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D49" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
@@ -2134,8 +2392,11 @@
       <c r="C50" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D50" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>59</v>
       </c>
@@ -2145,8 +2406,11 @@
       <c r="C51" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D51" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>61</v>
       </c>
@@ -2156,8 +2420,12 @@
       <c r="C52" t="s">
         <v>112</v>
       </c>
+      <c r="D52" t="s">
+        <v>388</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D52" xr:uid="{4E0D0A95-DEDA-4243-943F-4F8F00442EF6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2165,15 +2433,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F66BE2-8FA9-465B-9CB8-84C0ED0A8FDB}">
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.9453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5234375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2186,8 +2454,11 @@
       <c r="D1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>67</v>
       </c>
@@ -2197,8 +2468,11 @@
       <c r="C2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>0.60416666666666663</v>
       </c>
@@ -2208,8 +2482,11 @@
       <c r="C3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>0.59375</v>
       </c>
@@ -2219,8 +2496,11 @@
       <c r="C4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0.66666666666666663</v>
       </c>
@@ -2230,8 +2510,11 @@
       <c r="C5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>0.5</v>
       </c>
@@ -2241,8 +2524,11 @@
       <c r="C6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>73</v>
       </c>
@@ -2252,8 +2538,11 @@
       <c r="C7" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>0.45833333333333331</v>
       </c>
@@ -2263,8 +2552,11 @@
       <c r="C8" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E8" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>0.41666666666666669</v>
       </c>
@@ -2274,8 +2566,11 @@
       <c r="C9" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>0.375</v>
       </c>
@@ -2285,8 +2580,11 @@
       <c r="C10" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E10" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>0.33333333333333298</v>
       </c>
@@ -2296,8 +2594,11 @@
       <c r="C11" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E11" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>0.29166666666666602</v>
       </c>
@@ -2307,8 +2608,11 @@
       <c r="C12" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E12" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>0.25</v>
       </c>
@@ -2318,8 +2622,11 @@
       <c r="C13" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E13" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>0.20833333333333301</v>
       </c>
@@ -2329,8 +2636,11 @@
       <c r="C14" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E14" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>0.16666666666666699</v>
       </c>
@@ -2340,8 +2650,11 @@
       <c r="C15" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>0.125</v>
       </c>
@@ -2351,8 +2664,11 @@
       <c r="C16" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>8.3333333333333301E-2</v>
       </c>
@@ -2362,8 +2678,11 @@
       <c r="C17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>4.1666666666667303E-2</v>
       </c>
@@ -2373,8 +2692,11 @@
       <c r="C18" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>229</v>
       </c>
@@ -2384,8 +2706,11 @@
       <c r="D19" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>230</v>
       </c>
@@ -2395,8 +2720,11 @@
       <c r="D20" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>231</v>
       </c>
@@ -2406,8 +2734,11 @@
       <c r="D21" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>232</v>
       </c>
@@ -2417,8 +2748,11 @@
       <c r="D22" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>233</v>
       </c>
@@ -2428,8 +2762,11 @@
       <c r="D23" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>234</v>
       </c>
@@ -2439,8 +2776,11 @@
       <c r="D24" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>235</v>
       </c>
@@ -2450,8 +2790,11 @@
       <c r="D25" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>236</v>
       </c>
@@ -2461,8 +2804,11 @@
       <c r="D26" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>237</v>
       </c>
@@ -2472,8 +2818,11 @@
       <c r="D27" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>238</v>
       </c>
@@ -2483,8 +2832,11 @@
       <c r="D28" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>239</v>
       </c>
@@ -2494,8 +2846,11 @@
       <c r="D29" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>240</v>
       </c>
@@ -2504,6 +2859,20 @@
       </c>
       <c r="D30" t="s">
         <v>243</v>
+      </c>
+      <c r="E30" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" t="s">
+        <v>368</v>
+      </c>
+      <c r="E31" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -2515,14 +2884,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5DCFB58-E6A2-4ABA-BC82-6631C8630162}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.41796875" customWidth="1"/>
-    <col min="2" max="2" width="32.41796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="23.5234375" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>247</v>
       </c>
@@ -2536,7 +2905,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>298</v>
       </c>
@@ -2550,7 +2919,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>296</v>
       </c>
@@ -2564,7 +2933,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>294</v>
       </c>
@@ -2578,7 +2947,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>292</v>
       </c>
@@ -2592,7 +2961,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>291</v>
       </c>
@@ -2606,7 +2975,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>289</v>
       </c>
@@ -2620,7 +2989,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>288</v>
       </c>
@@ -2634,7 +3003,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>286</v>
       </c>
@@ -2648,7 +3017,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>284</v>
       </c>
@@ -2662,7 +3031,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>282</v>
       </c>
@@ -2676,7 +3045,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>280</v>
       </c>
@@ -2690,7 +3059,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>278</v>
       </c>
@@ -2704,7 +3073,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>276</v>
       </c>
@@ -2718,7 +3087,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>274</v>
       </c>
@@ -2732,7 +3101,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>272</v>
       </c>
@@ -2746,7 +3115,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>270</v>
       </c>
@@ -2760,7 +3129,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>268</v>
       </c>
@@ -2774,7 +3143,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -2788,7 +3157,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>264</v>
       </c>
@@ -2802,7 +3171,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>262</v>
       </c>
@@ -2816,7 +3185,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>260</v>
       </c>
@@ -2830,7 +3199,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>258</v>
       </c>
@@ -2844,7 +3213,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>256</v>
       </c>
@@ -2858,7 +3227,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>254</v>
       </c>
@@ -2872,7 +3241,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>249</v>
       </c>
@@ -2886,7 +3255,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>252</v>
       </c>
@@ -2900,7 +3269,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>316</v>
       </c>
@@ -2914,7 +3283,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>317</v>
       </c>
@@ -2928,7 +3297,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>318</v>
       </c>
@@ -2942,7 +3311,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>321</v>
       </c>
@@ -2956,7 +3325,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>324</v>
       </c>
@@ -2970,7 +3339,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>327</v>
       </c>
@@ -2991,20 +3360,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B39F442-7702-4133-AA1C-50B16E28B9D9}">
-  <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.89453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.3671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.1015625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.1015625" customWidth="1"/>
+    <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>134</v>
       </c>
@@ -3029,8 +3399,11 @@
       <c r="H1" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I1" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>139</v>
       </c>
@@ -3052,8 +3425,11 @@
       <c r="H2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>139</v>
       </c>
@@ -3075,8 +3451,11 @@
       <c r="H3" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -3101,8 +3480,11 @@
       <c r="H4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>139</v>
       </c>
@@ -3127,8 +3509,11 @@
       <c r="H5" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>139</v>
       </c>
@@ -3150,8 +3535,11 @@
       <c r="H6" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -3173,8 +3561,11 @@
       <c r="H7" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>139</v>
       </c>
@@ -3199,8 +3590,11 @@
       <c r="H8" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>139</v>
       </c>
@@ -3225,8 +3619,11 @@
       <c r="H9" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>139</v>
       </c>
@@ -3251,8 +3648,11 @@
       <c r="H10" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>139</v>
       </c>
@@ -3277,8 +3677,11 @@
       <c r="H11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I11" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -3303,8 +3706,11 @@
       <c r="H12" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>139</v>
       </c>
@@ -3329,8 +3735,11 @@
       <c r="H13" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>139</v>
       </c>
@@ -3355,8 +3764,11 @@
       <c r="H14" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -3381,8 +3793,11 @@
       <c r="H15" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -3407,8 +3822,11 @@
       <c r="H16" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>139</v>
       </c>
@@ -3433,8 +3851,11 @@
       <c r="H17" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>161</v>
       </c>
@@ -3459,8 +3880,11 @@
       <c r="H18" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I18" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>161</v>
       </c>
@@ -3485,8 +3909,11 @@
       <c r="H19" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>161</v>
       </c>
@@ -3511,8 +3938,11 @@
       <c r="H20" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>161</v>
       </c>
@@ -3537,8 +3967,11 @@
       <c r="H21" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>161</v>
       </c>
@@ -3563,8 +3996,11 @@
       <c r="H22" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>161</v>
       </c>
@@ -3589,8 +4025,11 @@
       <c r="H23" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>161</v>
       </c>
@@ -3615,8 +4054,11 @@
       <c r="H24" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I24" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>161</v>
       </c>
@@ -3641,8 +4083,11 @@
       <c r="H25" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I25" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>161</v>
       </c>
@@ -3667,8 +4112,11 @@
       <c r="H26" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>161</v>
       </c>
@@ -3693,8 +4141,11 @@
       <c r="H27" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>161</v>
       </c>
@@ -3719,8 +4170,11 @@
       <c r="H28" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I28" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>161</v>
       </c>
@@ -3745,8 +4199,11 @@
       <c r="H29" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I29" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>161</v>
       </c>
@@ -3771,8 +4228,11 @@
       <c r="H30" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>161</v>
       </c>
@@ -3797,8 +4257,11 @@
       <c r="H31" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I31" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>161</v>
       </c>
@@ -3823,8 +4286,11 @@
       <c r="H32" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>161</v>
       </c>
@@ -3849,8 +4315,11 @@
       <c r="H33" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>183</v>
       </c>
@@ -3875,8 +4344,11 @@
       <c r="H34" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I34" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>183</v>
       </c>
@@ -3901,8 +4373,11 @@
       <c r="H35" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>183</v>
       </c>
@@ -3927,8 +4402,11 @@
       <c r="H36" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>183</v>
       </c>
@@ -3953,8 +4431,11 @@
       <c r="H37" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>183</v>
       </c>
@@ -3979,8 +4460,11 @@
       <c r="H38" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I38" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>183</v>
       </c>
@@ -4005,8 +4489,11 @@
       <c r="H39" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>183</v>
       </c>
@@ -4031,8 +4518,11 @@
       <c r="H40" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>183</v>
       </c>
@@ -4057,8 +4547,11 @@
       <c r="H41" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>183</v>
       </c>
@@ -4083,8 +4576,11 @@
       <c r="H42" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I42" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>183</v>
       </c>
@@ -4109,8 +4605,11 @@
       <c r="H43" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>183</v>
       </c>
@@ -4135,8 +4634,11 @@
       <c r="H44" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I44" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>183</v>
       </c>
@@ -4161,8 +4663,11 @@
       <c r="H45" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I45" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>183</v>
       </c>
@@ -4187,8 +4692,11 @@
       <c r="H46" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I46" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>183</v>
       </c>
@@ -4213,8 +4721,11 @@
       <c r="H47" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>183</v>
       </c>
@@ -4239,8 +4750,11 @@
       <c r="H48" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I48" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>183</v>
       </c>
@@ -4263,6 +4777,9 @@
         <v>204</v>
       </c>
       <c r="H49" t="s">
+        <v>204</v>
+      </c>
+      <c r="I49" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4275,15 +4792,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE4A692-E4D1-4DEB-9164-719B5653CDBF}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.20703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.41796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.41796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4312,7 +4829,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>118</v>
       </c>
@@ -4326,7 +4843,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>119</v>
       </c>
@@ -4340,7 +4857,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>117</v>
       </c>
@@ -4354,7 +4871,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>120</v>
       </c>
@@ -4368,7 +4885,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>121</v>
       </c>
@@ -4379,7 +4896,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>122</v>
       </c>
@@ -4393,7 +4910,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>123</v>
       </c>
@@ -4407,7 +4924,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -4421,7 +4938,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>124</v>
       </c>
@@ -4435,7 +4952,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>126</v>
       </c>
